--- a/Assets/Data/Excel/BasicProperties.xlsx
+++ b/Assets/Data/Excel/BasicProperties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365EBFA9-B57E-452C-BDC1-C4B088C42626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36BA0E-F7C5-46BA-AC4E-089EE630B52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6720" yWindow="4785" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8715" yWindow="3600" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,9 +39,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>specialEffectId</t>
-  </si>
-  <si>
     <t>max_hp</t>
   </si>
   <si>
@@ -176,10 +173,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>外部使用的id</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>属性英语名</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -188,7 +181,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>特效类型</t>
+    <t>外部使用的id，对应属性系统的Enum</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>valueType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>数值类型</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -582,33 +583,33 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="C2" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>51</v>
@@ -619,13 +620,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="D4" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -633,13 +634,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="D5" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -647,13 +648,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -661,10 +662,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -675,13 +676,13 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -689,13 +690,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -703,13 +704,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -717,13 +718,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="D11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -731,13 +732,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -745,10 +746,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -759,13 +760,13 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D14" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -773,13 +774,13 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -787,13 +788,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="D16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -801,13 +802,13 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -815,13 +816,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="D18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -829,13 +830,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="D19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -843,13 +844,13 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="D20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
@@ -857,13 +858,13 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="D21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -871,13 +872,13 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="D22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
@@ -885,13 +886,13 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="D23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
@@ -899,10 +900,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>

--- a/Assets/Data/Excel/BasicProperties.xlsx
+++ b/Assets/Data/Excel/BasicProperties.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C36BA0E-F7C5-46BA-AC4E-089EE630B52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F856F20D-E334-4479-BAB5-C5B8D246A79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8715" yWindow="3600" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16785" yWindow="3255" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,15 +30,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>attrName</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
     <t>max_hp</t>
   </si>
   <si>
@@ -185,11 +176,22 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>valueType</t>
+    <t>数值类型</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>数值类型</t>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>AttrName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ValueType</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -574,45 +576,45 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -620,10 +622,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -634,10 +636,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -648,10 +650,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -662,10 +664,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -676,10 +678,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -690,10 +692,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -704,10 +706,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -718,10 +720,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -732,10 +734,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -746,10 +748,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -760,10 +762,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -774,10 +776,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -788,10 +790,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -802,10 +804,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -816,10 +818,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -830,10 +832,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
@@ -844,10 +846,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -858,10 +860,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -872,10 +874,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -886,10 +888,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -900,10 +902,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>

--- a/Assets/Data/Excel/BasicProperties.xlsx
+++ b/Assets/Data/Excel/BasicProperties.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\2DModulePlay\Assets\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F856F20D-E334-4479-BAB5-C5B8D246A79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBE61CA-F08B-4226-9F47-60A686965342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16785" yWindow="3255" windowWidth="13395" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -28,7 +25,37 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>AttrName</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ValueType</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>外部使用的id，对应属性系统的Enum</t>
+  </si>
+  <si>
+    <t>属性英语名</t>
+  </si>
+  <si>
+    <t>属性描述</t>
+  </si>
+  <si>
+    <t>数值类型</t>
+  </si>
   <si>
     <t>max_hp</t>
   </si>
@@ -156,43 +183,22 @@
     <t>消耗品回复</t>
   </si>
   <si>
-    <t>int</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性英语名</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>属性描述</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>外部使用的id，对应属性系统的Enum</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>数值类型</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>AttrName</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Description</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ValueType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>projectile_pierce</t>
+  </si>
+  <si>
+    <t>穿透次数</t>
+  </si>
+  <si>
+    <t>projectile_bounce</t>
+  </si>
+  <si>
+    <t>弹射次数</t>
+  </si>
+  <si>
+    <t>explosion_range_percent</t>
+  </si>
+  <si>
+    <t>爆炸范围增值</t>
   </si>
 </sst>
 </file>
@@ -285,7 +291,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -571,50 +577,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="18.125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -622,10 +631,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
@@ -636,10 +645,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -650,10 +659,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1">
         <v>1</v>
@@ -664,10 +673,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1">
         <v>0</v>
@@ -678,10 +687,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -692,10 +701,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1">
         <v>1</v>
@@ -706,10 +715,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1">
         <v>1</v>
@@ -720,10 +729,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1">
         <v>1</v>
@@ -734,10 +743,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1">
         <v>1</v>
@@ -748,10 +757,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
@@ -762,10 +771,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -776,10 +785,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -790,10 +799,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -804,10 +813,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -818,10 +827,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D18" s="1">
         <v>1</v>
@@ -832,10 +841,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
@@ -846,10 +855,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -860,10 +869,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -874,10 +883,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -888,10 +897,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D23" s="1">
         <v>1</v>
@@ -902,18 +911,60 @@
         <v>21</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>22</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>23</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>24</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>